--- a/AAII_Financials/Quarterly/CHT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>CHT</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1928800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1875800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2090700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1900200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1939900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1677200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1991900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1751000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1665800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1718400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2019300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1667400</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1204700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1164400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1387600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1194500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1195300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1027900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1331100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1108500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1024600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1077600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1345300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1051700</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>724000</v>
+      </c>
+      <c r="E10" s="3">
         <v>711400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>703000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>705700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>744600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>649300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>660800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>642500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>641200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>640800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>673900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>615800</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E12" s="3">
         <v>34900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>37600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>35100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>33900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -935,75 +955,81 @@
         <v>-100</v>
       </c>
       <c r="E14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="3">
         <v>-20200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>20800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E15" s="3">
         <v>283400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>287200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>290800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>304000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>266500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>268900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>276000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>270200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>275700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>288500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>274300</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1512000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1466100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1724400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1503300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1511100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1640700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1392500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1298600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1345600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1657300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1311200</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E18" s="3">
         <v>409700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>366200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>396900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>428800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>376300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>351200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>358500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>367300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>372900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>362000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>356300</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1107,101 +1140,108 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>707400</v>
+      </c>
+      <c r="E21" s="3">
         <v>692500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>651400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>689800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>736200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>644000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>625000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>635100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>638400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>648300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>647400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>634000</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2700</v>
       </c>
       <c r="I22" s="3">
         <v>2700</v>
@@ -1210,95 +1250,104 @@
         <v>2700</v>
       </c>
       <c r="K22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="L22" s="3">
         <v>2600</v>
       </c>
       <c r="M22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N22" s="3">
         <v>2800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>438600</v>
+      </c>
+      <c r="E23" s="3">
         <v>412200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>387900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>402100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>449000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>381600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>363900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>361700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>380100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>374900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>340600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>361600</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E24" s="3">
         <v>80500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>73900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>86400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>73000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>69400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>68800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>62200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>354100</v>
+      </c>
+      <c r="E26" s="3">
         <v>331700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>314100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>323300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>362600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>306400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>290900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>292300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>311200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>300400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>278500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>291500</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>334500</v>
+      </c>
+      <c r="E27" s="3">
         <v>316100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>296300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>309700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>347700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>294500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>274700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>283500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>302300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>293700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>269500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>282600</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>334500</v>
+      </c>
+      <c r="E33" s="3">
         <v>316100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>296300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>309700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>347700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>294500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>274700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>283500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>302300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>293700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>269500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>282600</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>334500</v>
+      </c>
+      <c r="E35" s="3">
         <v>316100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>296300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>309700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>347700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>294500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>274700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>283500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>302300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>293700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>269500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>282600</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1790,350 +1876,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1327100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1101700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1176500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>771800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1198000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>873000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1106200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>982800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1160900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1042500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1104000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>994600</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1125100</v>
+      </c>
+      <c r="E42" s="3">
         <v>952200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>654600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>467500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1272600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1053200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>661400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>409300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>929600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>819300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>606200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>302600</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1123200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1224100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1176300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1171400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1116600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>960100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1078300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>991800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>985900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>954500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1061700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>974300</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>636700</v>
+      </c>
+      <c r="E44" s="3">
         <v>548300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>487800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>521100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>485400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>415500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>429900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>464800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>429200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>422500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>448900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>500500</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E45" s="3">
         <v>122100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>121700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>131100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>112800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>70700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>74800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>79100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>80700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>66700</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4518900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4204700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3737700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3273500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4400800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3565000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3446300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3114600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3782400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3479200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3368500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3011400</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>592400</v>
+      </c>
+      <c r="E47" s="3">
         <v>583200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>588300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>581500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>602200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>526200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>510900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>459300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>444200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>460100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>453600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>383000</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>9145900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9171600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9519400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9670500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10127100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8953300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9174900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9259300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9114700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9326300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9908500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9272700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1779700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1821800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1903100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2013300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2154400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1942900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2022100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2136500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2139000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2223600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2373700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2308200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1123200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1108400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1073500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1051900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1083700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>938600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>931400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>842200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>808100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>815500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>774500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>737400</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>17401500</v>
+      </c>
+      <c r="E54" s="3">
         <v>17129900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17064900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16831600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18618700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16145600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16305400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16045600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16512800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16525800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17101000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15916800</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2354,236 +2484,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>360200</v>
+      </c>
+      <c r="E57" s="3">
         <v>432900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>507100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>441900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>380300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>321400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>541300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>389800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>302500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>306700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>469900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>409500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>263800</v>
+      </c>
+      <c r="E58" s="3">
         <v>309200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>195200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>212100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>512600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>392900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>383600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>402000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>170100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>172500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>185700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>182600</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2667500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1406400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1321200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1126200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2541400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1115000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1074900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>969900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2169700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1065900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1038300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1033300</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3692400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2557900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2513900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2182100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3817200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2190400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2437200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2118100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2961800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1905700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2146500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1961600</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>936900</v>
+      </c>
+      <c r="E61" s="3">
         <v>933800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1015500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1053400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>979800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>925100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>935100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>968000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1167800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1184800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1238800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1177700</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>395200</v>
+      </c>
+      <c r="E62" s="3">
         <v>400800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>398900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>411600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>436000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>392200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>412900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>395100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>386400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>397900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>430800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>5392100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4264600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4301700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4023900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5637400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3875500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4160700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3870600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4898800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3870100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4211600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3910900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>3634300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4544200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4305800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4127400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3979600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4357800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4124600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3916700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3552100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4456400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4344000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3875700</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>11523800</v>
+      </c>
+      <c r="E76" s="3">
         <v>12392500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12300400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12354500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12540500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11883300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11743500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11778800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11236900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12276100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12478200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11622900</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>334500</v>
+      </c>
+      <c r="E81" s="3">
         <v>316100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>296300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>309700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>347700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>294500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>274700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>283500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>302300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>293700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>269500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>282600</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E83" s="3">
         <v>250700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>252000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>258400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>252800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>257600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>269600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>256100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>264800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>268900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>267000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>648700</v>
+      </c>
+      <c r="E89" s="3">
         <v>347200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1018700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>530600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>558500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>389200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>899600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>646300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>464900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>441900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>805200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>665800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-166500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-142300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-331100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-190600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-208000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-162500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-388700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-181500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-160300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-157700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-387200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-220800</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-454300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-561700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>571600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-305300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-575300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-738400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>359500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-294300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-406200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-736900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37100</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3677,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>1272400</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>1162100</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>1133500</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,118 +4072,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-88400</v>
+      </c>
+      <c r="E100" s="3">
         <v>52400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1480900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-43400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-31800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1210900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-51700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1180700</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
       </c>
       <c r="M101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>219800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-53600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>427300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-377500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>204700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-216700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>153900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-204600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>134900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-551600</v>
       </c>
     </row>
